--- a/MATERIAL_IN_OUT/Template/UploadMaterInOut_A.xlsx
+++ b/MATERIAL_IN_OUT/Template/UploadMaterInOut_A.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70L4853\Desktop\a\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70K6885\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E428A23-35DF-4EA7-8289-BD9CFCFA66F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="8235"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,22 +19,34 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master(Ko Xóa)'!$A$1:$H$50</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>NGUYEN THI_Dao</author>
+    <author>NGUYEN NHU_Minh</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -48,7 +61,69 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="1" shapeId="0" xr:uid="{A8EC6788-2305-4CEE-BB97-0FE3B4E58EC2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>NGUYEN NHU_Minh:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Bộ phận tự điền</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{9BF479D2-CB8A-481D-AF24-AF1C5700A377}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>NGUYEN NHU_Minh:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Bộ phận bắt buộc phải điền</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{6C093821-3E40-4812-A057-7C64E5C662EA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>NGUYEN NHU_Minh: Bộ phận tự điền</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -62,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -91,7 +166,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="106">
   <si>
     <t>Sloc</t>
   </si>
@@ -388,13 +463,34 @@
   </si>
   <si>
     <t>Scrap mixing part560</t>
+  </si>
+  <si>
+    <t>Roh_Halb</t>
+  </si>
+  <si>
+    <t>Halb</t>
+  </si>
+  <si>
+    <t>STprice</t>
+  </si>
+  <si>
+    <t>NameCode</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>Namecost_costcentor</t>
+  </si>
+  <si>
+    <t>khong bat buoc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -430,8 +526,21 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,6 +550,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,10 +579,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -475,6 +586,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -754,105 +871,132 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="4"/>
-    <col min="7" max="7" width="13.7109375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" customWidth="1"/>
-    <col min="12" max="13" width="21" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" customWidth="1"/>
+    <col min="16" max="16" width="17.7109375" customWidth="1"/>
+    <col min="17" max="17" width="18.140625" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="J1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="O1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="P1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="Q1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="R1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <v>9</v>
+    <row r="2" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="1">
         <v>2020</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>5</v>
       </c>
-      <c r="E2">
+      <c r="F2">
+        <v>120000</v>
+      </c>
+      <c r="G2">
         <v>5.1566453999999998E-2</v>
       </c>
-      <c r="F2" s="2">
-        <v>201</v>
-      </c>
-      <c r="G2" s="2" t="str">
-        <f>VLOOKUP(F2,'Master(Ko Xóa)'!$F$2:$H$158,3,0)</f>
+      <c r="H2" s="2">
+        <v>201</v>
+      </c>
+      <c r="I2" s="2" t="str">
+        <f>VLOOKUP(H2,'Master(Ko Xóa)'!$F$2:$H$158,3,0)</f>
         <v>Out</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="N2" t="s">
         <v>16</v>
       </c>
-      <c r="L2" t="s">
+      <c r="P2" t="s">
         <v>19</v>
       </c>
-      <c r="M2" t="s">
+      <c r="Q2" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="2"/>
+      <c r="R2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -861,13 +1005,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>'Master(Ko Xóa)'!$O$2:$O$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F2</xm:sqref>
+          <xm:sqref>H2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>'Master(Ko Xóa)'!$A$2:$A$25</xm:f>
           </x14:formula1>
@@ -880,7 +1024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O50"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -931,9 +1075,9 @@
       <c r="N2" t="s">
         <v>22</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="str">
         <f>VLOOKUP(Sheet1!A2,'Master(Ko Xóa)'!$D$2:$K$158,8,0)</f>
-        <v>201</v>
+        <v>mpa</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -963,9 +1107,9 @@
         <f>F3</f>
         <v>202</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="str">
         <f>VLOOKUP(Sheet1!A2,'Master(Ko Xóa)'!$I$3:$J$147,2,0)</f>
-        <v>202</v>
+        <v>mpa</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -2114,7 +2258,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H50"/>
+  <autoFilter ref="A1:H50" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MATERIAL_IN_OUT/Template/UploadMaterInOut_A.xlsx
+++ b/MATERIAL_IN_OUT/Template/UploadMaterInOut_A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70K6885\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktops\code suport 2020\Dao\June.2022_MaterialTranfer\MATERIAL_IN_OUT\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E428A23-35DF-4EA7-8289-BD9CFCFA66F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EA1017-DF27-4F41-9E55-8D173D70EA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,6 +123,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{6124359F-64FB-4EE1-8ED9-A0E0DFD9A9E3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>NGUYEN NHU_Minh:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Bắt buộc phải nhập</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
@@ -483,7 +507,7 @@
     <t>Namecost_costcentor</t>
   </si>
   <si>
-    <t>khong bat buoc</t>
+    <t>Bat buoc</t>
   </si>
 </sst>
 </file>
@@ -607,6 +631,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/MATERIAL_IN_OUT/Template/UploadMaterInOut_A.xlsx
+++ b/MATERIAL_IN_OUT/Template/UploadMaterInOut_A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktops\code suport 2020\Dao\June.2022_MaterialTranfer\MATERIAL_IN_OUT\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70K6885\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EA1017-DF27-4F41-9E55-8D173D70EA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BCE14A-FB10-4F33-BF4F-9C8FA34962A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master(Ko Xóa)'!$A$1:$H$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$2</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -170,7 +171,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>B1: Chọn MvType sẽ lọc theo TypeRQ.</t>
+          <t>B1: Chọn MvType theo TypeRQ.</t>
         </r>
         <r>
           <rPr>
@@ -631,10 +632,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -976,7 +973,7 @@
     </row>
     <row r="2" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>14</v>
@@ -1032,16 +1029,10 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
-          <x14:formula1>
-            <xm:f>'Master(Ko Xóa)'!$O$2:$O$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>H2</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
-            <xm:f>'Master(Ko Xóa)'!$A$2:$A$25</xm:f>
+            <xm:f>'Master(Ko Xóa)'!$A$2:$A$34</xm:f>
           </x14:formula1>
           <xm:sqref>A2</xm:sqref>
         </x14:dataValidation>
@@ -1056,6 +1047,7 @@
   <dimension ref="A1:O50"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="5" max="5" width="45.5703125" customWidth="1"/>
     <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
   </cols>
@@ -1103,9 +1095,9 @@
       <c r="N2" t="s">
         <v>22</v>
       </c>
-      <c r="O2" t="str">
+      <c r="O2" t="e">
         <f>VLOOKUP(Sheet1!A2,'Master(Ko Xóa)'!$D$2:$K$158,8,0)</f>
-        <v>mpa</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -1135,9 +1127,9 @@
         <f>F3</f>
         <v>202</v>
       </c>
-      <c r="O3" t="str">
+      <c r="O3" t="e">
         <f>VLOOKUP(Sheet1!A2,'Master(Ko Xóa)'!$I$3:$J$147,2,0)</f>
-        <v>mpa</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -1166,7 +1158,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1194,7 +1186,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1218,7 +1210,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -1246,7 +1238,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -1270,7 +1262,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -1298,7 +1290,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1322,7 +1314,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -1350,7 +1342,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1374,7 +1366,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -1402,7 +1394,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1426,7 +1418,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -1454,7 +1446,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>15</v>
+        <v>13.1</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -1478,7 +1470,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="D17">
         <v>8</v>
@@ -1506,7 +1498,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>17</v>
+        <v>13.3</v>
       </c>
       <c r="D18">
         <v>9</v>
@@ -1530,7 +1522,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>18</v>
+        <v>13.4</v>
       </c>
       <c r="D19">
         <v>9</v>
@@ -1558,7 +1550,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D20">
         <v>10</v>
@@ -1582,7 +1574,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>20</v>
+        <v>15.1</v>
       </c>
       <c r="D21">
         <v>10</v>
@@ -1610,7 +1602,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21</v>
+        <v>15.2</v>
       </c>
       <c r="D22">
         <v>11</v>
@@ -1634,7 +1626,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>22</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="D23">
         <v>11</v>
@@ -1662,7 +1654,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>23</v>
+        <v>16.2</v>
       </c>
       <c r="D24">
         <v>12</v>
@@ -1686,7 +1678,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>25</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="D25">
         <v>12</v>
@@ -1713,6 +1705,9 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>17.2</v>
+      </c>
       <c r="D26">
         <v>13</v>
       </c>
@@ -1734,6 +1729,9 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>18.100000000000001</v>
+      </c>
       <c r="D27">
         <v>13</v>
       </c>
@@ -1759,6 +1757,9 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>18.2</v>
+      </c>
       <c r="D28">
         <v>14</v>
       </c>
@@ -1780,6 +1781,9 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>19</v>
+      </c>
       <c r="D29">
         <v>14</v>
       </c>
@@ -1805,6 +1809,9 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>20</v>
+      </c>
       <c r="D30">
         <v>15</v>
       </c>
@@ -1826,6 +1833,9 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>21</v>
+      </c>
       <c r="D31">
         <v>15</v>
       </c>
@@ -1851,6 +1861,9 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>22</v>
+      </c>
       <c r="D32">
         <v>16</v>
       </c>
@@ -1871,7 +1884,10 @@
         <v>201</v>
       </c>
     </row>
-    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>23</v>
+      </c>
       <c r="D33">
         <v>16</v>
       </c>
@@ -1896,7 +1912,10 @@
         <v>202</v>
       </c>
     </row>
-    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>24</v>
+      </c>
       <c r="D34">
         <v>16</v>
       </c>
@@ -1917,7 +1936,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D35">
         <v>17</v>
       </c>
@@ -1942,7 +1961,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D36">
         <v>17</v>
       </c>
@@ -1963,7 +1982,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D37">
         <v>18</v>
       </c>
@@ -1988,7 +2007,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D38">
         <v>18</v>
       </c>
@@ -2009,7 +2028,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D39">
         <v>19</v>
       </c>
@@ -2030,7 +2049,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D40">
         <v>19</v>
       </c>
@@ -2055,7 +2074,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D41">
         <v>20</v>
       </c>
@@ -2076,7 +2095,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D42">
         <v>20</v>
       </c>
@@ -2101,7 +2120,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="43" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D43">
         <v>21</v>
       </c>
@@ -2122,7 +2141,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="44" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D44">
         <v>21</v>
       </c>
@@ -2147,7 +2166,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="45" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D45">
         <v>22</v>
       </c>
@@ -2168,7 +2187,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="46" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D46">
         <v>22</v>
       </c>
@@ -2193,7 +2212,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="47" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D47">
         <v>23</v>
       </c>
@@ -2214,7 +2233,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D48">
         <v>23</v>
       </c>
